--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.847936693689849</v>
+        <v>0.8452524630835619</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0328854555575277</v>
+        <v>0.022295572805692</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.886603392782555</v>
+        <v>0.925440028538784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.119967580166158</v>
+        <v>0.372870581921771</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.718546723494759</v>
+        <v>0.96404592749758</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0076986691535798</v>
+        <v>0.0181912811071119</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8452524630835619</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="C2" t="n">
-        <v>0.022295572805692</v>
+        <v>0.0015437858087531</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.925440028538784</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="C3" t="n">
-        <v>0.372870581921771</v>
+        <v>0.0353115430734109</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.96404592749758</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0181912811071119</v>
+        <v>0.0034638333653721</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.988503117170494</v>
+        <v>0.09</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0015437858087531</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.86598189210379</v>
+        <v>0.066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0353115430734109</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.940958804337006</v>
+        <v>0.870534508464975</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0034638333653721</v>
+        <v>0.036685327279244</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/pvclust_summary.xlsx
@@ -450,10 +450,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09</v>
+        <v>0.988503117170494</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09</v>
+        <v>0.0015437858087531</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.066</v>
+        <v>0.86598189210379</v>
       </c>
       <c r="C3" t="n">
-        <v>0.066</v>
+        <v>0.0353115430734109</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.870534508464975</v>
+        <v>0.940958804337006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.036685327279244</v>
+        <v>0.0034638333653721</v>
       </c>
     </row>
   </sheetData>
